--- a/services_forms/015_detailed_food_menu--services_forms.xlsx
+++ b/services_forms/015_detailed_food_menu--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>food_status</t>
+          <t>food_status_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Food Status</t>
+          <t>Food Status 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>food_item</t>
+          <t>food_item_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Food Item</t>
+          <t>Food Item 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>food_description</t>
+          <t>food_description_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Food Description</t>
+          <t>Food Description 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>food_image</t>
+          <t>food_image_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Food Image</t>
+          <t>Food Image 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>availability</t>
+          <t>availability_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Availability</t>
+          <t>Availability 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>food_status_choices</t>
+          <t>food_status_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>food_status_choices</t>
+          <t>food_status_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>availability_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>availability_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
